--- a/output.xlsx
+++ b/output.xlsx
@@ -140,6 +140,86 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6096000" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,7 +521,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Protein_1</t>
+          <t>Insulin</t>
         </is>
       </c>
     </row>
@@ -1388,5 +1468,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>